--- a/Team-Data/2020-21/1-20-2020-21.xlsx
+++ b/Team-Data/2020-21/1-20-2020-21.xlsx
@@ -806,13 +806,13 @@
         <v>1.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG2" t="n">
         <v>16</v>
@@ -821,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="AI2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK2" t="n">
         <v>28</v>
@@ -848,10 +848,10 @@
         <v>2</v>
       </c>
       <c r="AR2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT2" t="n">
         <v>2</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
         <v>1.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE3" t="n">
         <v>7</v>
@@ -1027,10 +1027,10 @@
         <v>17</v>
       </c>
       <c r="AQ3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS3" t="n">
         <v>24</v>
@@ -1039,10 +1039,10 @@
         <v>12</v>
       </c>
       <c r="AU3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW3" t="n">
         <v>6</v>
@@ -1060,7 +1060,7 @@
         <v>15</v>
       </c>
       <c r="BB3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC3" t="n">
         <v>12</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
         <v>5.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Z4" t="n">
         <v>18.5</v>
@@ -1173,7 +1173,7 @@
         <v>1</v>
       </c>
       <c r="AE4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF4" t="n">
         <v>9</v>
@@ -1185,7 +1185,7 @@
         <v>18</v>
       </c>
       <c r="AI4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ4" t="n">
         <v>21</v>
@@ -1200,7 +1200,7 @@
         <v>13</v>
       </c>
       <c r="AN4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO4" t="n">
         <v>6</v>
@@ -1215,7 +1215,7 @@
         <v>23</v>
       </c>
       <c r="AS4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT4" t="n">
         <v>10</v>
@@ -1224,10 +1224,10 @@
         <v>8</v>
       </c>
       <c r="AV4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX4" t="n">
         <v>8</v>
@@ -1245,7 +1245,7 @@
         <v>3</v>
       </c>
       <c r="BC4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -1355,10 +1355,10 @@
         <v>4</v>
       </c>
       <c r="AE5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG5" t="n">
         <v>20</v>
@@ -1385,22 +1385,22 @@
         <v>14</v>
       </c>
       <c r="AO5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ5" t="n">
         <v>22</v>
       </c>
       <c r="AR5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS5" t="n">
         <v>21</v>
       </c>
       <c r="AT5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU5" t="n">
         <v>1</v>
@@ -1418,13 +1418,13 @@
         <v>22</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA5" t="n">
         <v>21</v>
       </c>
       <c r="BB5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC5" t="n">
         <v>15</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -1537,10 +1537,10 @@
         <v>4</v>
       </c>
       <c r="AE6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG6" t="n">
         <v>20</v>
@@ -1579,10 +1579,10 @@
         <v>25</v>
       </c>
       <c r="AS6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU6" t="n">
         <v>14</v>
@@ -1603,7 +1603,7 @@
         <v>27</v>
       </c>
       <c r="BA6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB6" t="n">
         <v>4</v>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -1716,13 +1716,13 @@
         <v>-4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG7" t="n">
         <v>16</v>
@@ -1758,13 +1758,13 @@
         <v>30</v>
       </c>
       <c r="AR7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU7" t="n">
         <v>20</v>
@@ -1776,16 +1776,16 @@
         <v>2</v>
       </c>
       <c r="AX7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY7" t="n">
         <v>18</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>19</v>
       </c>
       <c r="AZ7" t="n">
         <v>9</v>
       </c>
       <c r="BA7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB7" t="n">
         <v>30</v>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -1898,19 +1898,19 @@
         <v>0.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG8" t="n">
         <v>16</v>
       </c>
       <c r="AH8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI8" t="n">
         <v>28</v>
@@ -1919,10 +1919,10 @@
         <v>23</v>
       </c>
       <c r="AK8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM8" t="n">
         <v>7</v>
@@ -1931,7 +1931,7 @@
         <v>25</v>
       </c>
       <c r="AO8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP8" t="n">
         <v>7</v>
@@ -1961,16 +1961,16 @@
         <v>21</v>
       </c>
       <c r="AY8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA8" t="n">
         <v>6</v>
       </c>
       <c r="BB8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC8" t="n">
         <v>14</v>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -2002,160 +2002,160 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
         <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="I9" t="n">
-        <v>42.8</v>
+        <v>43.1</v>
       </c>
       <c r="J9" t="n">
-        <v>88.7</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.483</v>
+        <v>0.479</v>
       </c>
       <c r="L9" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="M9" t="n">
-        <v>34.3</v>
+        <v>34.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0.377</v>
+        <v>0.373</v>
       </c>
       <c r="O9" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="P9" t="n">
-        <v>22.7</v>
+        <v>22.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.739</v>
+        <v>0.748</v>
       </c>
       <c r="R9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="S9" t="n">
-        <v>32.2</v>
+        <v>32.7</v>
       </c>
       <c r="T9" t="n">
-        <v>43.2</v>
+        <v>44.2</v>
       </c>
       <c r="U9" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="V9" t="n">
         <v>14.4</v>
       </c>
       <c r="W9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="X9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA9" t="n">
-        <v>22.4</v>
+        <v>21.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>115.4</v>
+        <v>115.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AE9" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AF9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AJ9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AK9" t="n">
         <v>6</v>
       </c>
       <c r="AL9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AM9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AO9" t="n">
         <v>17</v>
       </c>
       <c r="AP9" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AQ9" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AR9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AS9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AT9" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AU9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV9" t="n">
         <v>13</v>
       </c>
       <c r="AW9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY9" t="n">
         <v>9</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>10</v>
       </c>
       <c r="AZ9" t="n">
         <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BB9" t="n">
         <v>5</v>
       </c>
       <c r="BC9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -2229,16 +2229,16 @@
         <v>11.1</v>
       </c>
       <c r="S10" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T10" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U10" t="n">
         <v>24.5</v>
       </c>
       <c r="V10" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W10" t="n">
         <v>8.4</v>
@@ -2262,7 +2262,7 @@
         <v>-4.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE10" t="n">
         <v>28</v>
@@ -2295,16 +2295,16 @@
         <v>21</v>
       </c>
       <c r="AO10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ10" t="n">
         <v>10</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS10" t="n">
         <v>30</v>
@@ -2316,10 +2316,10 @@
         <v>19</v>
       </c>
       <c r="AV10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX10" t="n">
         <v>22</v>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE11" t="n">
         <v>11</v>
@@ -2462,7 +2462,7 @@
         <v>21</v>
       </c>
       <c r="AJ11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK11" t="n">
         <v>23</v>
@@ -2480,7 +2480,7 @@
         <v>5</v>
       </c>
       <c r="AP11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ11" t="n">
         <v>11</v>
@@ -2492,28 +2492,28 @@
         <v>14</v>
       </c>
       <c r="AT11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU11" t="n">
         <v>11</v>
       </c>
       <c r="AV11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW11" t="n">
         <v>17</v>
       </c>
       <c r="AX11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ11" t="n">
         <v>29</v>
       </c>
       <c r="BA11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB11" t="n">
         <v>13</v>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -2626,13 +2626,13 @@
         <v>-2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE12" t="n">
         <v>27</v>
       </c>
       <c r="AF12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG12" t="n">
         <v>27</v>
@@ -2641,13 +2641,13 @@
         <v>4</v>
       </c>
       <c r="AI12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL12" t="n">
         <v>9</v>
@@ -2677,10 +2677,10 @@
         <v>23</v>
       </c>
       <c r="AU12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW12" t="n">
         <v>15</v>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2808,7 @@
         <v>3.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2820,7 +2820,7 @@
         <v>7</v>
       </c>
       <c r="AH13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI13" t="n">
         <v>3</v>
@@ -2847,7 +2847,7 @@
         <v>25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR13" t="n">
         <v>24</v>
@@ -2883,7 +2883,7 @@
         <v>11</v>
       </c>
       <c r="BC13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
         <v>20</v>
       </c>
       <c r="AX14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3187,7 @@
         <v>19</v>
       </c>
       <c r="AI15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ15" t="n">
         <v>17</v>
@@ -3208,7 +3208,7 @@
         <v>15</v>
       </c>
       <c r="AP15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ15" t="n">
         <v>15</v>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
         <v>41.6</v>
       </c>
       <c r="J16" t="n">
-        <v>92.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="K16" t="n">
         <v>0.452</v>
@@ -3318,13 +3318,13 @@
         <v>0.765</v>
       </c>
       <c r="R16" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S16" t="n">
         <v>34.8</v>
       </c>
       <c r="T16" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="U16" t="n">
         <v>27.2</v>
@@ -3354,7 +3354,7 @@
         <v>-0.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
@@ -3366,7 +3366,7 @@
         <v>12</v>
       </c>
       <c r="AH16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI16" t="n">
         <v>11</v>
@@ -3378,13 +3378,13 @@
         <v>17</v>
       </c>
       <c r="AL16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM16" t="n">
         <v>27</v>
       </c>
-      <c r="AM16" t="n">
-        <v>28</v>
-      </c>
       <c r="AN16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO16" t="n">
         <v>28</v>
@@ -3396,7 +3396,7 @@
         <v>13</v>
       </c>
       <c r="AR16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS16" t="n">
         <v>16</v>
@@ -3405,7 +3405,7 @@
         <v>11</v>
       </c>
       <c r="AU16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV16" t="n">
         <v>12</v>
@@ -3414,7 +3414,7 @@
         <v>1</v>
       </c>
       <c r="AX16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY16" t="n">
         <v>29</v>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -3536,13 +3536,13 @@
         <v>-3.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE17" t="n">
         <v>23</v>
       </c>
       <c r="AF17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG17" t="n">
         <v>23</v>
@@ -3605,7 +3605,7 @@
         <v>23</v>
       </c>
       <c r="BA17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB17" t="n">
         <v>18</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         <v>15.9</v>
       </c>
       <c r="M18" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="N18" t="n">
         <v>0.403</v>
@@ -3700,7 +3700,7 @@
         <v>9.1</v>
       </c>
       <c r="X18" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y18" t="n">
         <v>5.1</v>
@@ -3721,7 +3721,7 @@
         <v>4</v>
       </c>
       <c r="AE18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF18" t="n">
         <v>5</v>
@@ -3748,7 +3748,7 @@
         <v>4</v>
       </c>
       <c r="AN18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO18" t="n">
         <v>25</v>
@@ -3760,13 +3760,13 @@
         <v>24</v>
       </c>
       <c r="AR18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU18" t="n">
         <v>9</v>
@@ -3778,7 +3778,7 @@
         <v>5</v>
       </c>
       <c r="AX18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY18" t="n">
         <v>13</v>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
         <v>-10.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE19" t="n">
         <v>28</v>
@@ -3927,10 +3927,10 @@
         <v>24</v>
       </c>
       <c r="AM19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO19" t="n">
         <v>21</v>
@@ -3954,7 +3954,7 @@
         <v>21</v>
       </c>
       <c r="AV19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW19" t="n">
         <v>12</v>
@@ -3969,10 +3969,10 @@
         <v>19</v>
       </c>
       <c r="BA19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC19" t="n">
         <v>30</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -4004,160 +4004,160 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
         <v>5</v>
       </c>
       <c r="F20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>0.417</v>
+        <v>0.385</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
       </c>
       <c r="I20" t="n">
-        <v>39.9</v>
+        <v>40.2</v>
       </c>
       <c r="J20" t="n">
-        <v>85.8</v>
+        <v>86.5</v>
       </c>
       <c r="K20" t="n">
-        <v>0.466</v>
+        <v>0.464</v>
       </c>
       <c r="L20" t="n">
-        <v>10.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>30.4</v>
+        <v>30.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.334</v>
+        <v>0.327</v>
       </c>
       <c r="O20" t="n">
-        <v>17.8</v>
+        <v>17.2</v>
       </c>
       <c r="P20" t="n">
-        <v>24.8</v>
+        <v>24</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.717</v>
+        <v>0.715</v>
       </c>
       <c r="R20" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="S20" t="n">
-        <v>36.8</v>
+        <v>36.1</v>
       </c>
       <c r="T20" t="n">
-        <v>48.3</v>
+        <v>47.5</v>
       </c>
       <c r="U20" t="n">
-        <v>22.8</v>
+        <v>22.4</v>
       </c>
       <c r="V20" t="n">
-        <v>16.3</v>
+        <v>15.6</v>
       </c>
       <c r="W20" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X20" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>107.8</v>
+        <v>107.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>-1</v>
+        <v>-2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AE20" t="n">
         <v>23</v>
       </c>
       <c r="AF20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AG20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AI20" t="n">
         <v>18</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL20" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AM20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN20" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AO20" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AP20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ20" t="n">
         <v>28</v>
       </c>
       <c r="AR20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AS20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AT20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AV20" t="n">
         <v>24</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>26</v>
       </c>
       <c r="AW20" t="n">
         <v>18</v>
       </c>
       <c r="AX20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ20" t="n">
         <v>1</v>
       </c>
       <c r="BA20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB20" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BC20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4270,7 @@
         <v>11</v>
       </c>
       <c r="AF21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG21" t="n">
         <v>15</v>
@@ -4300,13 +4300,13 @@
         <v>22</v>
       </c>
       <c r="AP21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ21" t="n">
         <v>19</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>18</v>
-      </c>
       <c r="AR21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS21" t="n">
         <v>11</v>
@@ -4333,13 +4333,13 @@
         <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB21" t="n">
         <v>29</v>
       </c>
       <c r="BC21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -4368,34 +4368,34 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E22" t="n">
         <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5</v>
+        <v>0.462</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>39</v>
+        <v>38.8</v>
       </c>
       <c r="J22" t="n">
-        <v>87</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.448</v>
+        <v>0.446</v>
       </c>
       <c r="L22" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="M22" t="n">
-        <v>38.8</v>
+        <v>39.2</v>
       </c>
       <c r="N22" t="n">
         <v>0.33</v>
@@ -4404,85 +4404,85 @@
         <v>15.2</v>
       </c>
       <c r="P22" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.725</v>
+        <v>0.719</v>
       </c>
       <c r="R22" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="S22" t="n">
-        <v>37.8</v>
+        <v>37.4</v>
       </c>
       <c r="T22" t="n">
-        <v>45</v>
+        <v>44.7</v>
       </c>
       <c r="U22" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V22" t="n">
-        <v>14.8</v>
+        <v>15.1</v>
       </c>
       <c r="W22" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X22" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z22" t="n">
-        <v>19.2</v>
+        <v>18.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>106</v>
+        <v>105.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>-6.1</v>
+        <v>-7</v>
       </c>
       <c r="AD22" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AE22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF22" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AG22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AI22" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AJ22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AL22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM22" t="n">
         <v>5</v>
       </c>
       <c r="AN22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO22" t="n">
         <v>26</v>
       </c>
       <c r="AP22" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AQ22" t="n">
         <v>27</v>
@@ -4491,37 +4491,37 @@
         <v>29</v>
       </c>
       <c r="AS22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AT22" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AU22" t="n">
         <v>26</v>
       </c>
       <c r="AV22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX22" t="n">
         <v>16</v>
       </c>
-      <c r="AW22" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>15</v>
-      </c>
       <c r="AY22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA22" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BB22" t="n">
         <v>27</v>
       </c>
       <c r="BC22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -4631,10 +4631,10 @@
         <v>4</v>
       </c>
       <c r="AE23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG23" t="n">
         <v>20</v>
@@ -4652,7 +4652,7 @@
         <v>29</v>
       </c>
       <c r="AL23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM23" t="n">
         <v>25</v>
@@ -4691,7 +4691,7 @@
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ23" t="n">
         <v>2</v>
@@ -4703,7 +4703,7 @@
         <v>28</v>
       </c>
       <c r="BC23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4813,7 @@
         <v>4</v>
       </c>
       <c r="AE24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF24" t="n">
         <v>5</v>
@@ -4843,7 +4843,7 @@
         <v>17</v>
       </c>
       <c r="AO24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP24" t="n">
         <v>10</v>
@@ -4855,7 +4855,7 @@
         <v>17</v>
       </c>
       <c r="AS24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT24" t="n">
         <v>6</v>
@@ -4867,7 +4867,7 @@
         <v>28</v>
       </c>
       <c r="AW24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX24" t="n">
         <v>1</v>
@@ -4885,7 +4885,7 @@
         <v>10</v>
       </c>
       <c r="BC24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -4992,7 +4992,7 @@
         <v>3.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE25" t="n">
         <v>11</v>
@@ -5010,7 +5010,7 @@
         <v>16</v>
       </c>
       <c r="AJ25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK25" t="n">
         <v>13</v>
@@ -5028,7 +5028,7 @@
         <v>23</v>
       </c>
       <c r="AP25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ25" t="n">
         <v>4</v>
@@ -5052,7 +5052,7 @@
         <v>29</v>
       </c>
       <c r="AX25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY25" t="n">
         <v>2</v>
@@ -5061,13 +5061,13 @@
         <v>23</v>
       </c>
       <c r="BA25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB25" t="n">
         <v>20</v>
       </c>
       <c r="BC25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -5204,13 +5204,13 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO26" t="n">
         <v>7</v>
       </c>
       <c r="AP26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ26" t="n">
         <v>3</v>
@@ -5222,7 +5222,7 @@
         <v>19</v>
       </c>
       <c r="AT26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU26" t="n">
         <v>28</v>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
         <v>10</v>
       </c>
       <c r="AJ27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK27" t="n">
         <v>11</v>
@@ -5401,7 +5401,7 @@
         <v>15</v>
       </c>
       <c r="AS27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT27" t="n">
         <v>27</v>
@@ -5410,7 +5410,7 @@
         <v>16</v>
       </c>
       <c r="AV27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW27" t="n">
         <v>28</v>
@@ -5425,7 +5425,7 @@
         <v>14</v>
       </c>
       <c r="BA27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB27" t="n">
         <v>9</v>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
         <v>1</v>
       </c>
       <c r="AK28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL28" t="n">
         <v>25</v>
@@ -5583,7 +5583,7 @@
         <v>16</v>
       </c>
       <c r="AS28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT28" t="n">
         <v>9</v>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -5720,16 +5720,16 @@
         <v>1.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
       </c>
       <c r="AF29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH29" t="n">
         <v>19</v>
@@ -5738,7 +5738,7 @@
         <v>22</v>
       </c>
       <c r="AJ29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK29" t="n">
         <v>24</v>
@@ -5750,13 +5750,13 @@
         <v>1</v>
       </c>
       <c r="AN29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO29" t="n">
         <v>16</v>
       </c>
       <c r="AP29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ29" t="n">
         <v>7</v>
@@ -5768,7 +5768,7 @@
         <v>22</v>
       </c>
       <c r="AT29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU29" t="n">
         <v>18</v>
@@ -5777,7 +5777,7 @@
         <v>14</v>
       </c>
       <c r="AW29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX29" t="n">
         <v>4</v>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -5824,94 +5824,94 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F30" t="n">
         <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.714</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>40.6</v>
+        <v>40.8</v>
       </c>
       <c r="J30" t="n">
-        <v>88</v>
+        <v>87.8</v>
       </c>
       <c r="K30" t="n">
-        <v>0.462</v>
+        <v>0.465</v>
       </c>
       <c r="L30" t="n">
-        <v>16.2</v>
+        <v>16.5</v>
       </c>
       <c r="M30" t="n">
-        <v>40.7</v>
+        <v>41.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.397</v>
+        <v>0.401</v>
       </c>
       <c r="O30" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="P30" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="R30" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S30" t="n">
-        <v>38.2</v>
+        <v>38.5</v>
       </c>
       <c r="T30" t="n">
-        <v>49.3</v>
+        <v>49.6</v>
       </c>
       <c r="U30" t="n">
-        <v>22.9</v>
+        <v>23.3</v>
       </c>
       <c r="V30" t="n">
         <v>15.5</v>
       </c>
       <c r="W30" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="X30" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y30" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>18.8</v>
+        <v>18.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>110.5</v>
+        <v>111.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AE30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF30" t="n">
         <v>1</v>
       </c>
       <c r="AG30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH30" t="n">
         <v>19</v>
@@ -5920,10 +5920,10 @@
         <v>14</v>
       </c>
       <c r="AJ30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AL30" t="n">
         <v>1</v>
@@ -5938,13 +5938,13 @@
         <v>30</v>
       </c>
       <c r="AP30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ30" t="n">
         <v>29</v>
       </c>
       <c r="AR30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS30" t="n">
         <v>1</v>
@@ -5953,7 +5953,7 @@
         <v>1</v>
       </c>
       <c r="AU30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV30" t="n">
         <v>22</v>
@@ -5962,22 +5962,22 @@
         <v>30</v>
       </c>
       <c r="AX30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY30" t="n">
         <v>12</v>
       </c>
       <c r="AZ30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA30" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BB30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
@@ -6090,7 +6090,7 @@
         <v>28</v>
       </c>
       <c r="AF31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG31" t="n">
         <v>28</v>
@@ -6135,7 +6135,7 @@
         <v>24</v>
       </c>
       <c r="AU31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV31" t="n">
         <v>5</v>
@@ -6153,7 +6153,7 @@
         <v>30</v>
       </c>
       <c r="BA31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB31" t="n">
         <v>1</v>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-20-2020-21</t>
+          <t>2021-01-20</t>
         </is>
       </c>
     </row>
